--- a/store/Jul-2026/Mail Attachment/LinkedIn_Report_28-Jul-2026.xlsx
+++ b/store/Jul-2026/Mail Attachment/LinkedIn_Report_28-Jul-2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989204</t>
+          <t>WTI-20260728-3990746</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAPAN KAUR</t>
+          <t>SHARADHA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-24 19:00:00</t>
+          <t>2026-07-28 12:30:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9910910059</t>
+          <t>9840677632</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>sapkaur@linkedin.com</t>
+          <t>shasrinivasan@linkedin.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989405</t>
+          <t>WTI-20260728-3990739</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -551,22 +551,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EASHA NOPANY</t>
+          <t>NEHA TAMBE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-27 19:00:00</t>
+          <t>2026-07-28 17:00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9925027870</t>
+          <t>8879166492</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>linkedin.mum@wti.co.in</t>
+          <t>nkisantambe@linkedin.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -594,32 +594,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989391</t>
+          <t>WTI-20260728-3990971</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DARSHANA KANDALKAR</t>
+          <t>NIKHIL SAXENA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-27 21:00:00</t>
+          <t>2026-07-28 17:00:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9892854339</t>
+          <t>9810995672</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>linkedin.mum@wti.co.in</t>
+          <t>nsaxena@linkedin.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -647,32 +647,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989409</t>
+          <t>WTI-20260728-3990794</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MAHESH PRABHU</t>
+          <t>RITESH KHANDELWAL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-27 21:00:00</t>
+          <t>2026-07-28 17:30:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9322531352</t>
+          <t>9899099885</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>linkedin.mum@wti.co.in</t>
+          <t>rikhandelwal@linkedin.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -700,32 +700,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989394</t>
+          <t>WTI-20260728-3990831</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SNEHA DHARMISHT BANSAL</t>
+          <t>SHARADHA SRINIVASAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-27 21:00:00</t>
+          <t>2026-07-28 18:00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9967484113</t>
+          <t>9840677632</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>linkedin.mum@wti.co.in</t>
+          <t>shasrinivasan@linkedin.com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>Chennai Hub</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -753,7 +753,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989398</t>
+          <t>WTI-20260728-3990886</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUJIT SOMAN</t>
+          <t>ANURADHA RAY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-27 21:00:00</t>
+          <t>2026-07-28 18:15:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9819595556</t>
+          <t>9819717303</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>linkedin.mum@wti.co.in</t>
+          <t>anray@linkedin.com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -806,32 +806,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989397</t>
+          <t>WTI-20260728-3991005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MANU SHANKARAN POTTI</t>
+          <t>SHREYOSHI CHOUDHURY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-27 21:15:00</t>
+          <t>2026-07-28 20:00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8390514841</t>
+          <t>8335821039</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>linkedin.mum@wti.co.in</t>
+          <t>shchoudhury@linkedin.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -859,7 +859,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989388</t>
+          <t>WTI-20260728-3990722</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -869,22 +869,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MIHIR MEHTA</t>
+          <t>E CHAKRADHAR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-27 21:30:00</t>
+          <t>2026-07-29 05:00:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9820212204</t>
+          <t>9019653550</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>linkedin.mum@wti.co.in</t>
+          <t>echakradhar@linkedin.com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -894,17 +894,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -912,32 +912,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989732</t>
+          <t>WTI-20260728-3990864</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MARK ANDERSON</t>
+          <t>ANKIT JOSHI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-28 04:50:00</t>
+          <t>2026-07-29 05:15:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+353863498435</t>
+          <t>9818022132</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>kgrobel@linkedin.com</t>
+          <t>ankjoshi@linkedin.com</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -965,32 +965,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989737</t>
+          <t>WTI-20260728-3990815</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MARK ANDERSON</t>
+          <t>AMANPREET CHUGH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-28 07:00:00</t>
+          <t>2026-07-29 06:00:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+353863498435</t>
+          <t>9999951841</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>kgrobel@linkedin.com</t>
+          <t>amachugh@linkedin.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1018,32 +1018,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990278</t>
+          <t>WTI-20260728-3990975</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DHARAVI DASSANI</t>
+          <t>SAGAR MAINI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-28 07:00:00</t>
+          <t>2026-07-29 06:00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9591750535</t>
+          <t>9990856195</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ddassani@linkedin.com</t>
+          <t>smaini@linkedin.com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1071,32 +1071,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990390</t>
+          <t>WTI-20260728-3990882</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANIRUDH DUREHA</t>
+          <t>ANURAG CHAUHAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-28 07:00:00</t>
+          <t>2026-07-29 06:30:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9899233705</t>
+          <t>9540071883</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>adureha@linkedin.com</t>
+          <t>anchauhan@linkedin.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990093</t>
+          <t>WTI-20260728-3991010</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PRATIK JAIN</t>
+          <t>NIDHI SISODIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-28 08:00:00</t>
+          <t>2026-07-29 07:15:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9987733037</t>
+          <t>9930138639</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>pjain@linkedin.com</t>
+          <t>nisisodia@linkedin.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990366</t>
+          <t>WTI-20260728-3990820</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1187,22 +1187,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NIPUN OBEROI</t>
+          <t>PRITYUSH HALDAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-28 08:30:00</t>
+          <t>2026-07-29 08:15:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8860087407</t>
+          <t>9649869329</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>noberoi@linkedin.com</t>
+          <t>phaldar@linkedin.com</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990247</t>
+          <t>WTI-20260728-3990764</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KASHI VISWANATH KOSURI</t>
+          <t>E CHAKRADHAR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-28 08:30:00</t>
+          <t>2026-07-29 08:30:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8328484046</t>
+          <t>9019653550</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>kkosuri@linkedin.com</t>
+          <t>echakradhar@linkedin.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Hyderabad Hub</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1283,32 +1283,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989928</t>
+          <t>WTI-20260728-3990916</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANURADHA RAY</t>
+          <t>ADESH KISHINCHANDANI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-28 08:30:00</t>
+          <t>2026-07-29 10:15:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9819717303</t>
+          <t>9819360915</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>anray@linkedin.com</t>
+          <t>akishinchandani@linkedin.com</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1318,17 +1318,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1336,7 +1336,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990064</t>
+          <t>WTI-20260728-3991133</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1346,22 +1346,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JOMY SAJAN</t>
+          <t>HARSH RAJ GOSWAMI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-28 08:30:00</t>
+          <t>2026-07-29 11:00:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8800130363</t>
+          <t>9576569196</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>jsajan@linkedin.com</t>
+          <t>hgoswami@linkedin.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1389,32 +1389,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990391</t>
+          <t>WTI-20260728-3990976</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HITARTH VASANI</t>
+          <t>ANURAG CHAUHAN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-28 09:00:00</t>
+          <t>2026-07-29 12:45:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9004799797</t>
+          <t>9540071883</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>hvasani@linkedin.com</t>
+          <t>anchauhan@linkedin.com</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1424,17 +1424,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1442,32 +1442,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990258</t>
+          <t>WTI-20260728-3991022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MANAV SHAH</t>
+          <t>NIDHI SISODIA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-28 09:00:00</t>
+          <t>2026-07-29 17:00:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8980906025</t>
+          <t>9930138639</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>manshah@linkedin.com</t>
+          <t>nisisodia@linkedin.com</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Hyderabad Hub</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990292</t>
+          <t>WTI-20260728-3990991</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ANKIT JAIN</t>
+          <t>DEEPIKA SHARMA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-28 09:00:00</t>
+          <t>2026-07-29 22:45:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7574842024</t>
+          <t>9811460605</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ajain5@linkedin.com</t>
+          <t>desharma@linkedin.com</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1548,32 +1548,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990302</t>
+          <t>WTI-20260728-3991238</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GAUTAM SHARMA</t>
+          <t>MAHESH PRABHU</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-28 09:00:00</t>
+          <t>2026-07-30 07:30:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8800020988</t>
+          <t>9322531352</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>gautsharma@linkedin.com</t>
+          <t>mprabhu@linkedin.com</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1583,17 +1583,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1601,32 +1601,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989320</t>
+          <t>WTI-20260728-3990762</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PREETI KAUR BHATIA</t>
+          <t>ANKITA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-28 09:15:00</t>
+          <t>2026-07-30 08:00:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9999984589</t>
+          <t>8652260988</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>prbhatia@linkedin.com</t>
+          <t>anvishwakarma@linkedin.com</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1654,32 +1654,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WTI-20260727-3989769</t>
+          <t>WTI-20260728-3990918</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MIHIR KAPADIA</t>
+          <t>ANURAG CHAUHAN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-28 09:30:00</t>
+          <t>2026-07-30 08:00:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9820202920</t>
+          <t>9540071883</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>mikapadia@linkedin.com</t>
+          <t>anchauhan@linkedin.com</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1689,17 +1689,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1707,32 +1707,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990316</t>
+          <t>WTI-20260728-3991128</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KUNAL MUKHI</t>
+          <t>HARSH RAJ GOSWAMI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-28 09:30:00</t>
+          <t>2026-07-30 08:45:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7875180878</t>
+          <t>9576569196</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>kmukhi@linkedin.com</t>
+          <t>hgoswami@linkedin.com</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1760,32 +1760,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990311</t>
+          <t>WTI-20260728-3991240</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NESS BILLIMORIA</t>
+          <t>MAHESH PRABHU</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-28 09:30:00</t>
+          <t>2026-07-31 07:00:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9920137831</t>
+          <t>9322531352</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>nbillimoria@linkedin.com</t>
+          <t>mprabhu@linkedin.com</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990461</t>
+          <t>WTI-20260728-3991146</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1823,22 +1823,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAURABH SINGH</t>
+          <t>HARSH RAJ GOSWAMI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-28 10:00:00</t>
+          <t>2026-07-31 10:30:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8368058612</t>
+          <t>9576569196</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>saurabhsingh@linkedin.com</t>
+          <t>hgoswami@linkedin.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1848,17 +1848,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Noida</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1866,7 +1866,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990216</t>
+          <t>WTI-20260728-3991049</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1876,22 +1876,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RAMAN SAWNEY</t>
+          <t>NIKITA JADHAV</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-28 10:00:00</t>
+          <t>2026-07-31 14:00:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>9873683564</t>
+          <t>7499780657</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>rsinghsawhney@linkedin.com</t>
+          <t>nijadhav@linkedin.com</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1915,1119 +1915,6 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3989938</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>NIKITA TEVETIA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-07-28 11:00:00</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>9210003681</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ntevetia@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2445</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3990008</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>PALLAVI KAR</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-07-28 11:00:00</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>9650254463</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>pkar@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990662</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SURBHI GULATI ARORA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-07-28 12:30:00</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>9871071148</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>sugulati@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2502</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990609</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>NIVEDITA CHANANA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-07-28 13:00:00</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>8879576633</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>nchanana@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Mumbai Hub</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2706</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3990297</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>VISHAL PAL</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-07-28 13:00:00</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>7046167879</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>vpal@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Pune Hub 1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3990084</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMRUTA KOLEKAR</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-07-28 13:00:00</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>9373840675</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>akolekar@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Pune Hub 1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3990317</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AKASH ARORA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-07-28 13:15:00</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>9022919015</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>akarora@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2514</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990611</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>KRISHNA CHINTA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-07-28 13:30:00</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>7337888843</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>kchinta@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Hyderabad Hub</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2770</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3989988</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>NEHA SHETTY</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-07-28 14:00:00</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>9987090157</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>neshetty@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Mumbai Hub</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3990321</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AKASH ARORA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-07-28 19:00:00</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>9022919015</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>akarora@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Mumbai Hub</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2514</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990375</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SHREE AATHITHYAN</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-07-28 19:00:00</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>9944895329</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>saathithyan@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Chennai Hub</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990642</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AARUSHI AGGARWAL</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-07-28 19:45:00</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>9650038270</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>aaaggarwal@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2518</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3989345</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SHANTANU SUBHASH PATHAK</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-07-28 20:30:00</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>9820276736</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>spathak@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2517</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990377</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>SHREE AATHITHYAN</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-07-28 23:15:00</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>9944895329</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>saathithyan@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Dispatched</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990379</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>SHREE AATHITHYAN</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-07-29 06:30:00</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>9944895329</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>saathithyan@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3989678</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>MIHIR MEHTA</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026-07-29 09:15:00</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>9820212204</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>mimehta@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2716</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>WTI-20260727-3990207</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>VIDHI NAGPAL</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-07-29 09:45:00</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>9769988771</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>vviveknagpal@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990389</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>NEHA TAMBE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-07-29 10:30:00</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>8879166492</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>nkisantambe@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Mumbai Hub</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990654</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>NIKITA JADHAV</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-07-29 12:45:00</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>7499780657</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>nijadhav@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Mumbai Hub</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990380</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>SHREE AATHITHYAN</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-07-29 21:00:00</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>9944895329</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>saathithyan@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Chennai Hub</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>WTI-20260728-3990620</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>KELLY ALVARADO-YOUNG</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-07-31 23:35:00</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>+16314956005</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>kalvaradoyoung@linkedin.com</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>5125</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
